--- a/docs/finances/COSTS.xlsx
+++ b/docs/finances/COSTS.xlsx
@@ -9,9 +9,10 @@
   </bookViews>
   <sheets>
     <sheet name="已花成本" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="月成本预估" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="AI Token 成本" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="单位经济学" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="支出明细" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="月成本预估" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="AI Token 成本" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="单位经济学" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="194">
   <si>
     <t xml:space="preserve">开发期已花成本（截至 2026-04-29）</t>
   </si>
@@ -40,7 +41,7 @@
     <t xml:space="preserve">开发者</t>
   </si>
   <si>
-    <t xml:space="preserve">工程师</t>
+    <t xml:space="preserve">4 个月开发：1 月 MVP 脚手架；2 月 auth+orders+RBAC；3 月 products+pricing+ML 定价；4 月 AI 助手+i18n+demo seed</t>
   </si>
   <si>
     <r>
@@ -72,7 +73,64 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Cursor / Claude Code / Codex </t>
+      <t xml:space="preserve">Cursor $20/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个月 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ Claude Code beta × </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">几个月 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ Codex </t>
     </r>
     <r>
       <rPr>
@@ -88,13 +146,13 @@
     <t xml:space="preserve">服务器（阿里云 HK）</t>
   </si>
   <si>
-    <t xml:space="preserve">实例</t>
+    <t xml:space="preserve">4C8G 轻量实例 $32/月 × 6 期（4-9 月）+ 几次试错重启</t>
   </si>
   <si>
     <t xml:space="preserve">域名 + DNS</t>
   </si>
   <si>
-    <t xml:space="preserve">备用域名 + Cloudflare 免费层试用</t>
+    <t xml:space="preserve">citur.com 试注 + 备用 .cn 域名 + Cloudflare 免费层 DNS</t>
   </si>
   <si>
     <t xml:space="preserve">GitHub / CI</t>
@@ -117,26 +175,74 @@
         <rFont val="PingFang SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">分钟、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Codespaces </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="PingFang SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">偶尔用</t>
+      <t xml:space="preserve">分钟数（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CI/lint/test </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">流水线 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">~30k </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分钟）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">偶尔 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Codespaces</t>
     </r>
   </si>
   <si>
@@ -161,13 +267,13 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">早期对比 Claude vs GPT 选模型</t>
+    <t xml:space="preserve">早期对比 GPT-5-mini / GPT-4o / Claude Sonnet 4.6；tool-use 调试；Prompt 迭代</t>
   </si>
   <si>
     <t xml:space="preserve">杂项</t>
   </si>
   <si>
-    <t xml:space="preserve">图床（Unsplash CDN）、字体</t>
+    <t xml:space="preserve">Unsplash CDN 流量 + Google Fonts 商用授权 + 越南语人工校对</t>
   </si>
   <si>
     <t xml:space="preserve">图标 / 设计素材</t>
@@ -181,42 +287,125 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Figma </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="PingFang SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">订阅 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="PingFang SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">一些图标</t>
+      <t xml:space="preserve">Figma Professional $15/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">几个月 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ Iconify Pro </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">一次性</t>
     </r>
   </si>
   <si>
     <t xml:space="preserve">预留 buffer</t>
   </si>
   <si>
-    <t xml:space="preserve">重启 / 调错 / 数据库迁移期间小额</t>
+    <t xml:space="preserve">试错容器重启、Prisma migration 回退、bug 期间多跑的 AI 调用</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OpenRouter / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">其他 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LLM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">实验</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">合计（已花）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">支出明细（按时间倒序）— 每笔具体花在哪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">注：所有金额为估算（无真实发票对照）。每月底再来加新行。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">日期</t>
+  </si>
+  <si>
+    <t xml:space="preserve">供应商 / 项目</t>
+  </si>
+  <si>
+    <t xml:space="preserve">金额 (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">具体买了什么</t>
+  </si>
+  <si>
+    <t xml:space="preserve">工时备注</t>
   </si>
   <si>
     <r>
@@ -228,7 +417,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">── 2026-05 </t>
+      <t xml:space="preserve">═══ 2026-01</t>
     </r>
     <r>
       <rPr>
@@ -238,7 +427,7 @@
         <rFont val="PingFang SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">增量（截至 </t>
+      <t xml:space="preserve">：</t>
     </r>
     <r>
       <rPr>
@@ -249,7 +438,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">5/20</t>
+      <t xml:space="preserve">MVP </t>
     </r>
     <r>
       <rPr>
@@ -259,18 +448,475 @@
         <rFont val="PingFang SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）──</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="PingFang SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">开发者（</t>
+      <t xml:space="preserve">脚手架阶段 ═══</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">工程师本人</t>
+  </si>
+  <si>
+    <t xml:space="preserve">搭建 monorepo：backend / sales-web / admin-web / miniprogram；Prisma schema 初版</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~40h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-20</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">编码工具</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Cursor Pro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">月费 1 期（年付 $192）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">认证模块（JWT + refresh token + RBAC 4 角色 + 微信扫码 stub）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">═══ 2026-02</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：核心订单流程 ═══</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-05</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Order + OrderItem + Passenger </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">模型；状态机 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个状态 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ ALLOWED_TRANSITIONS</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">~32h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">航班搜索 + 座位库存原子扣减 (CAS) + 退款报价计算器</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~36h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-18</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Claude Code </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">订阅</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">试用 Anthropic 官方 IDE 集成（按使用量）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">代理 3 级层级 (Agent.tier + parentAgentId) + 佣金分账逻辑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~28h</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">═══ 2026-03</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：产品 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&amp; ML </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">定价 ═══</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-04</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Hotels + Transfers + Visas + Bundles </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">产品 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CRUD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">mockData + Unsplash </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">选图</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">动态定价引擎：DateRanking (A/B/C/D) × 余位阶梯 (18 buckets)；PricingService</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OpenAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OpenAI API</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GPT-5-mini vs GPT-4o vs Claude Sonnet 4.6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">横向 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">benchmark</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；选型</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unsplash + Google Fonts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">酒店/接送/签证产品图（25 张 hero）+ Inter / Noto Sans 商用授权</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">服务器</t>
+  </si>
+  <si>
+    <t xml:space="preserve">阿里云 HK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">首月 4C8G 轻量 + 试部署</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">结算单 + 月度报表 + 多语言 i18n (zh/en/vi) 基础</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">═══ 2026-04</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">助手 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上线准备 ═══</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-02</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">助手 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
     </r>
     <r>
       <rPr>
@@ -289,47 +935,536 @@
         <rFont val="PingFang SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">月增量）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="PingFang SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周开发：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PNR </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="PingFang SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">导出 </t>
+      <t xml:space="preserve">个 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">tool (search_flights/hotels/transfers/visas/bundles + propose_order)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-08</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">助手 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Prompt </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">反复迭代 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">多轮 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">tool-use </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">调试 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ token </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">用量优化</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">订单管理批量操作 + 审计日志中文化 + 强制改状态</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">设计</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figma + Iconify</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Figma Pro 4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个月 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">($60) + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">一些图标包 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">($70)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">第 2 月 + 配置 Docker Compose + nginx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">域名</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Namecheap + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">阿里云</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">citur.com </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">试注 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">备用 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.cn </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">域名 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ Cloudflare </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">免费层 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DNS</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">小程序（Taro 4.0.9）+ 微信支付 sandbox + 取消政策</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GitHub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GitHub Actions</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">流水线（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30k </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分钟）：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">lint / test / build / docker push</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">人工翻译</t>
+  </si>
+  <si>
+    <t xml:space="preserve">越南语 / 英语 i18n 文案人工校对</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-27</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Codex </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">订阅</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">试用 + 月费 × 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-28</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Demo seed 6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">单 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">演示包 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(DECK.pptx + 4 docx + COSTS.xlsx) + i18n bug </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">修</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cursor + Claude Code</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月份订阅</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Docker </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">重启错误 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ migration </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回退 </t>
     </r>
     <r>
       <rPr>
@@ -348,48 +1483,27 @@
         <rFont val="PingFang SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">护照打包 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="PingFang SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">待办系统 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="PingFang SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">客户字段扩展</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">容器重建 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ bug </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">期间多跑的 </t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -407,8 +1521,217 @@
         <rFont val="PingFang SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">编码工具订阅（</t>
-    </r>
+      <t xml:space="preserve">调用</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">额外用量 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">偶尔 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Codespaces</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Unsplash / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">字体补</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">产品图替换 + 字体加 weight</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">═══ 2026-05</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <i val="true"/>
+        <sz val="11"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：反馈驱动迭代 ═══</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-05</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">路由表 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ RBAC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">跨域代理 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ agents.routes </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">完整覆盖</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">~24h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">小程序 build 修 (webpack@5.91 pin + Node 22) + dev.ts 指 staging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~20h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">第 3 月（包月）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">测试 staging AI 调用（地区屏蔽前的小额）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OpenRouter</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OpenRouter </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="PingFang SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">实验</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">替代 OpenAI 时的 OpenRouter / DeepSeek 测试预算</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -426,271 +1749,23 @@
         <rFont val="PingFang SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">月）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Cursor + Claude Code </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="PingFang SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月费</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="PingFang SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">服务器（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="PingFang SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月 阿里云 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="PingFang SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4C8G </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="PingFang SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">包月</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI API</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="PingFang SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">mock </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="PingFang SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">兜底 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="PingFang SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">测试）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">OpenAI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="PingFang SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">试错调用；本地 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">mock </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="PingFang SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">上线后骤减</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">OpenRouter / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="PingFang SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">其他 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">LLM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="PingFang SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">实验</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="PingFang SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">替代 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">OpenAI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="PingFang SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">时的测试预算</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">合计（已花）</t>
+      <t xml:space="preserve">月份订阅</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">反馈 wave 1：PNR Excel / 护照 zip / 待办系统 / 17 字段扩展 / 拼房 / claim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~60h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">═══ 合计 ═══</t>
+  </si>
+  <si>
+    <t xml:space="preserve">累计</t>
   </si>
   <si>
     <t xml:space="preserve">投产后月成本预估（3 阶段）</t>
@@ -836,9 +1911,6 @@
   </si>
   <si>
     <t xml:space="preserve">对话量×单价；A: 50-200/天 ｜ B: 500-1500/天 ｜ C: 3000-8000/天</t>
-  </si>
-  <si>
-    <t xml:space="preserve">服务器</t>
   </si>
   <si>
     <t xml:space="preserve">阿里云 HK 4C8G → 8C16G + 备份机 → 主从 + worker</t>
@@ -1198,18 +2270,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
-    <numFmt numFmtId="166" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
-    <numFmt numFmtId="167" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
-    <numFmt numFmtId="168" formatCode="#,##0"/>
-    <numFmt numFmtId="169" formatCode="0.0%"/>
-    <numFmt numFmtId="170" formatCode="0.00"/>
-    <numFmt numFmtId="171" formatCode="\¥#,##0"/>
-    <numFmt numFmtId="172" formatCode="0.0\×"/>
+    <numFmt numFmtId="166" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
+    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="0.00"/>
+    <numFmt numFmtId="170" formatCode="\¥#,##0"/>
+    <numFmt numFmtId="171" formatCode="0.0\×"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1252,10 +2323,11 @@
       <color theme="1"/>
       <name val="PingFang SC"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1263,22 +2335,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="PingFang SC"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <i val="true"/>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <i val="true"/>
-      <sz val="11"/>
       <name val="PingFang SC"/>
       <family val="2"/>
     </font>
@@ -1300,6 +2356,36 @@
       <i val="true"/>
       <sz val="10"/>
       <color rgb="FF666666"/>
+      <name val="PingFang SC"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <i val="true"/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <i val="true"/>
+      <sz val="11"/>
+      <name val="PingFang SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <i val="true"/>
+      <sz val="11"/>
       <name val="PingFang SC"/>
       <family val="2"/>
       <charset val="1"/>
@@ -1384,14 +2470,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE7E8D1"/>
-        <bgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFE7E8D1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFE7E8D1"/>
+        <fgColor rgb="FFE7E8D1"/>
+        <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -1444,12 +2530,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1469,39 +2559,43 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1509,43 +2603,71 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1553,35 +2675,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1840,204 +2934,163 @@
   <dimension ref="A1:C19"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="60"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>4100</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="B4" s="5" t="n">
+        <f aca="false">SUMIF(支出明细!B:B,"开发者",支出明细!D:D)</f>
+        <v>6600</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="B5" s="5" t="n">
+        <f aca="false">SUMIF(支出明细!B:B,"AI 编码工具",支出明细!D:D)</f>
+        <v>250</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="B6" s="5" t="n">
+        <f aca="false">SUMIF(支出明细!B:B,"服务器",支出明细!D:D)</f>
+        <v>96</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="5" t="n">
+        <f aca="false">SUMIF(支出明细!B:B,"域名",支出明细!D:D)</f>
         <v>50</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="5" t="n">
+        <f aca="false">SUMIF(支出明细!B:B,"GitHub",支出明细!D:D)</f>
         <v>80</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="4" t="n">
-        <v>250</v>
-      </c>
-      <c r="C9" s="6" t="s">
+      <c r="B9" s="5" t="n">
+        <f aca="false">SUMIF(支出明细!B:B,"OpenAI",支出明细!D:D)</f>
+        <v>280</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="5" t="n">
+        <f aca="false">SUMIF(支出明细!B:B,"杂项",支出明细!D:D)</f>
         <v>173</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="5" t="n">
+        <f aca="false">SUMIF(支出明细!B:B,"设计",支出明细!D:D)</f>
         <v>130</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="5" t="n">
+        <f aca="false">SUMIF(支出明细!B:B,"预留 buffer",支出明细!D:D)</f>
         <v>510</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-    </row>
-    <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="B13" s="7" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="8" t="n">
-        <v>1300</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" s="10" t="n">
-        <f aca="false">SUM(B4:B18)</f>
-        <v>7205</v>
-      </c>
-      <c r="C19" s="11"/>
-    </row>
+      <c r="B14" s="9" t="n">
+        <f aca="false">支出明细!D46</f>
+        <v>8219</v>
+      </c>
+      <c r="C14" s="10"/>
+    </row>
+    <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A13:C13"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2054,209 +3107,800 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F46"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+    </row>
+    <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+    </row>
+    <row r="6" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
+      <c r="F6" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-    </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="13" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="B7" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="C7" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="D7" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>550</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E6" s="6" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+    </row>
+    <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>450</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>350</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+    </row>
+    <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>450</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+    </row>
+    <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>450</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>130</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D29" s="13" t="n">
         <v>40</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="4" t="n">
+      <c r="E29" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F29" s="6"/>
+    </row>
+    <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F30" s="6"/>
+    </row>
+    <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D31" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D33" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F33" s="6"/>
+    </row>
+    <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D34" s="13" t="n">
+        <v>510</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F34" s="6"/>
+    </row>
+    <row r="35" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D35" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D36" s="13" t="n">
+        <v>33</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F36" s="6"/>
+    </row>
+    <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+    </row>
+    <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D38" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D39" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D40" s="13" t="n">
         <v>32</v>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>250</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="4" t="n">
+      <c r="E40" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F40" s="6"/>
+    </row>
+    <row r="41" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D41" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F41" s="6"/>
+    </row>
+    <row r="42" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D42" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="D8" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>600</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="E11" s="5" t="s">
+      <c r="E42" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F42" s="6"/>
+    </row>
+    <row r="43" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D43" s="13" t="n">
         <v>50</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" s="10" t="n">
-        <f aca="false">SUM(B6:B12)</f>
-        <v>72</v>
-      </c>
-      <c r="C13" s="10" t="n">
-        <f aca="false">SUM(C6:C12)</f>
-        <v>870</v>
-      </c>
-      <c r="D13" s="10" t="n">
-        <f aca="false">SUM(D6:D12)</f>
-        <v>4750</v>
-      </c>
-      <c r="E13" s="11"/>
-    </row>
-    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14" s="15" t="n">
-        <f aca="false">B13*12</f>
-        <v>864</v>
-      </c>
-      <c r="C14" s="15" t="n">
-        <f aca="false">C13*12</f>
-        <v>10440</v>
-      </c>
-      <c r="D14" s="15" t="n">
-        <f aca="false">D13*12</f>
-        <v>57000</v>
-      </c>
+      <c r="E43" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F43" s="6"/>
+    </row>
+    <row r="44" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D44" s="13" t="n">
+        <v>750</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="B45" s="14"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="9" t="n">
+        <f aca="false">SUM(D5:D45)</f>
+        <v>8219</v>
+      </c>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A3:E3"/>
+  <mergeCells count="8">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A45:F45"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2273,318 +3917,537 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="50"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+    </row>
+    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>550</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>600</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="B13" s="9" t="n">
+        <f aca="false">SUM(B6:B12)</f>
+        <v>72</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <f aca="false">SUM(C6:C12)</f>
+        <v>870</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <f aca="false">SUM(D6:D12)</f>
+        <v>4750</v>
+      </c>
+      <c r="E13" s="10"/>
+    </row>
+    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="B14" s="17" t="n">
+        <f aca="false">B13*12</f>
+        <v>864</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <f aca="false">C13*12</f>
+        <v>10440</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <f aca="false">D13*12</f>
+        <v>57000</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:D35"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
+      <c r="A1" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" s="17"/>
+      <c r="A3" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="B3" s="19"/>
     </row>
     <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="18" t="n">
+      <c r="A4" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B4" s="20" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" s="18" t="n">
+      <c r="A5" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B5" s="20" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="18" t="n">
+      <c r="A6" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B6" s="20" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
+      <c r="A8" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9" s="19" t="n">
+      <c r="A9" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B9" s="21" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="19" t="n">
+      <c r="A10" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B10" s="21" t="n">
         <v>9000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B11" s="19" t="n">
+      <c r="A11" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B11" s="21" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B12" s="19" t="n">
+      <c r="A12" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B12" s="21" t="n">
         <v>2500</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
+      <c r="A14" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="20" t="s">
-        <v>66</v>
+      <c r="A15" s="22" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="B16" s="22" t="n">
+      <c r="A16" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="B16" s="24" t="n">
         <f aca="false">B9*B4/1000000</f>
         <v>0.03</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="B17" s="22" t="n">
+      <c r="A17" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="B17" s="24" t="n">
         <f aca="false">B12*B5/1000000</f>
         <v>0.0375</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="B18" s="24" t="n">
+      <c r="A18" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="B18" s="26" t="n">
         <f aca="false">B16+B17</f>
         <v>0.0675</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="20" t="s">
-        <v>70</v>
+      <c r="A20" s="22" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" s="22" t="n">
+      <c r="A21" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="B21" s="24" t="n">
         <f aca="false">B10*B6/1000000</f>
         <v>0.0027</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="B22" s="22" t="n">
+      <c r="A22" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="B22" s="24" t="n">
         <f aca="false">B11*B4/1000000</f>
         <v>0.003</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="B23" s="22" t="n">
+      <c r="A23" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="B23" s="24" t="n">
         <f aca="false">B12*B5/1000000</f>
         <v>0.0375</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" s="24" t="n">
+      <c r="A24" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="B24" s="26" t="n">
         <f aca="false">B21+B22+B23</f>
         <v>0.0432</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="B25" s="25" t="n">
+      <c r="A25" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="B25" s="27" t="n">
         <f aca="false">1-B24/B18</f>
         <v>0.36</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
+      <c r="A27" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
     </row>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="n">
+      <c r="A28" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="B29" s="26" t="n">
+      <c r="B29" s="28" t="n">
         <f aca="false">A29*30</f>
         <v>1500</v>
       </c>
-      <c r="C29" s="27" t="n">
+      <c r="C29" s="29" t="n">
         <f aca="false">B29*$B$24</f>
         <v>64.8</v>
       </c>
-      <c r="D29" s="27" t="n">
+      <c r="D29" s="29" t="n">
         <f aca="false">C29*12</f>
         <v>777.6</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="21" t="n">
         <v>200</v>
       </c>
-      <c r="B30" s="26" t="n">
+      <c r="B30" s="28" t="n">
         <f aca="false">A30*30</f>
         <v>6000</v>
       </c>
-      <c r="C30" s="27" t="n">
+      <c r="C30" s="29" t="n">
         <f aca="false">B30*$B$24</f>
         <v>259.2</v>
       </c>
-      <c r="D30" s="27" t="n">
+      <c r="D30" s="29" t="n">
         <f aca="false">C30*12</f>
         <v>3110.4</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="19" t="n">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="21" t="n">
         <v>500</v>
       </c>
-      <c r="B31" s="26" t="n">
+      <c r="B31" s="28" t="n">
         <f aca="false">A31*30</f>
         <v>15000</v>
       </c>
-      <c r="C31" s="27" t="n">
+      <c r="C31" s="29" t="n">
         <f aca="false">B31*$B$24</f>
         <v>648</v>
       </c>
-      <c r="D31" s="27" t="n">
+      <c r="D31" s="29" t="n">
         <f aca="false">C31*12</f>
         <v>7776</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19" t="n">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21" t="n">
         <v>1000</v>
       </c>
-      <c r="B32" s="26" t="n">
+      <c r="B32" s="28" t="n">
         <f aca="false">A32*30</f>
         <v>30000</v>
       </c>
-      <c r="C32" s="27" t="n">
+      <c r="C32" s="29" t="n">
         <f aca="false">B32*$B$24</f>
         <v>1296</v>
       </c>
-      <c r="D32" s="27" t="n">
+      <c r="D32" s="29" t="n">
         <f aca="false">C32*12</f>
         <v>15552</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="19" t="n">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21" t="n">
         <v>2000</v>
       </c>
-      <c r="B33" s="26" t="n">
+      <c r="B33" s="28" t="n">
         <f aca="false">A33*30</f>
         <v>60000</v>
       </c>
-      <c r="C33" s="27" t="n">
+      <c r="C33" s="29" t="n">
         <f aca="false">B33*$B$24</f>
         <v>2592</v>
       </c>
-      <c r="D33" s="27" t="n">
+      <c r="D33" s="29" t="n">
         <f aca="false">C33*12</f>
         <v>31104</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="19" t="n">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="21" t="n">
         <v>5000</v>
       </c>
-      <c r="B34" s="26" t="n">
+      <c r="B34" s="28" t="n">
         <f aca="false">A34*30</f>
         <v>150000</v>
       </c>
-      <c r="C34" s="27" t="n">
+      <c r="C34" s="29" t="n">
         <f aca="false">B34*$B$24</f>
         <v>6480</v>
       </c>
-      <c r="D34" s="27" t="n">
+      <c r="D34" s="29" t="n">
         <f aca="false">C34*12</f>
         <v>77760</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="19" t="n">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21" t="n">
         <v>8000</v>
       </c>
-      <c r="B35" s="26" t="n">
+      <c r="B35" s="28" t="n">
         <f aca="false">A35*30</f>
         <v>240000</v>
       </c>
-      <c r="C35" s="27" t="n">
+      <c r="C35" s="29" t="n">
         <f aca="false">B35*$B$24</f>
         <v>10368</v>
       </c>
-      <c r="D35" s="27" t="n">
+      <c r="D35" s="29" t="n">
         <f aca="false">C35*12</f>
         <v>124416</v>
       </c>
@@ -2607,7 +4470,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2615,235 +4478,235 @@
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="8.66796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="1" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="A1" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
+      <c r="A3" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="B5" s="28" t="n">
+      <c r="A5" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="B5" s="30" t="n">
         <v>0.14</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B6" s="29" t="n">
+      <c r="A6" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6" s="31" t="n">
         <v>0.08</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>89</v>
+      <c r="A8" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B9" s="19" t="n">
+      <c r="A9" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B9" s="21" t="n">
         <v>100</v>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="21" t="n">
         <v>3500</v>
       </c>
-      <c r="D9" s="30" t="n">
+      <c r="D9" s="32" t="n">
         <f aca="false">B9*C9</f>
         <v>350000</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="E9" s="32" t="n">
         <f aca="false">D9*$B$6</f>
         <v>28000</v>
       </c>
-      <c r="F9" s="27" t="n">
+      <c r="F9" s="29" t="n">
         <f aca="false">E9*$B$5</f>
         <v>3920</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="B10" s="19" t="n">
+      <c r="A10" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B10" s="21" t="n">
         <v>1000</v>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="21" t="n">
         <v>3800</v>
       </c>
-      <c r="D10" s="30" t="n">
+      <c r="D10" s="32" t="n">
         <f aca="false">B10*C10</f>
         <v>3800000</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="E10" s="32" t="n">
         <f aca="false">D10*$B$6</f>
         <v>304000</v>
       </c>
-      <c r="F10" s="27" t="n">
+      <c r="F10" s="29" t="n">
         <f aca="false">E10*$B$5</f>
         <v>42560</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="B11" s="19" t="n">
+      <c r="A11" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B11" s="21" t="n">
         <v>5000</v>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="21" t="n">
         <v>4000</v>
       </c>
-      <c r="D11" s="30" t="n">
+      <c r="D11" s="32" t="n">
         <f aca="false">B11*C11</f>
         <v>20000000</v>
       </c>
-      <c r="E11" s="30" t="n">
+      <c r="E11" s="32" t="n">
         <f aca="false">D11*$B$6</f>
         <v>1600000</v>
       </c>
-      <c r="F11" s="27" t="n">
+      <c r="F11" s="29" t="n">
         <f aca="false">E11*$B$5</f>
         <v>224000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
+      <c r="A14" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F15" s="2"/>
+      <c r="A15" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B16" s="31" t="n">
+      <c r="A16" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B16" s="33" t="n">
         <f aca="false">F9</f>
         <v>3920</v>
       </c>
-      <c r="C16" s="31" t="n">
+      <c r="C16" s="33" t="n">
         <f aca="false">月成本预估!C13</f>
         <v>870</v>
       </c>
-      <c r="D16" s="32" t="n">
+      <c r="D16" s="34" t="n">
         <f aca="false">B16/C16</f>
         <v>4.50574712643678</v>
       </c>
-      <c r="E16" s="33" t="n">
+      <c r="E16" s="35" t="n">
         <f aca="false">E9/D9</f>
         <v>0.08</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="B17" s="31" t="n">
+      <c r="A17" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B17" s="33" t="n">
         <f aca="false">F10</f>
         <v>42560</v>
       </c>
-      <c r="C17" s="31" t="n">
+      <c r="C17" s="33" t="n">
         <f aca="false">月成本预估!D13</f>
         <v>4750</v>
       </c>
-      <c r="D17" s="32" t="n">
+      <c r="D17" s="34" t="n">
         <f aca="false">B17/C17</f>
         <v>8.96</v>
       </c>
-      <c r="E17" s="33" t="n">
+      <c r="E17" s="35" t="n">
         <f aca="false">E10/D10</f>
         <v>0.08</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="B18" s="31" t="n">
+      <c r="A18" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B18" s="33" t="n">
         <f aca="false">F11</f>
         <v>224000</v>
       </c>
-      <c r="C18" s="31" t="n">
+      <c r="C18" s="33" t="n">
         <f aca="false">月成本预估!D13*1.5</f>
         <v>7125</v>
       </c>
-      <c r="D18" s="32" t="n">
+      <c r="D18" s="34" t="n">
         <f aca="false">B18/C18</f>
         <v>31.4385964912281</v>
       </c>
-      <c r="E18" s="33" t="n">
+      <c r="E18" s="35" t="n">
         <f aca="false">E11/D11</f>
         <v>0.08</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
+      <c r="A20" s="36" t="s">
+        <v>193</v>
+      </c>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="4">
